--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104606_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104606_W17.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8866</v>
+        <v>6.641</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4329</v>
+        <v>7.2068</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4537</v>
+        <v>-0.5658</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2703</v>
+        <v>2.5348</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2379</v>
+        <v>1.7209</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9675</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8956</v>
+        <v>4.1338</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7836</v>
+        <v>1.7507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.112</v>
+        <v>2.3832</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6252</v>
+        <v>-1.599</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4542</v>
+        <v>-0.0298</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0795</v>
+        <v>-1.5692</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.8211</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8865</v>
+        <v>1.9499</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7129</v>
+        <v>1.5393</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1736</v>
+        <v>0.4105</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9566</v>
+        <v>2.1563</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>3.3547</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.217</v>
+        <v>6.2706</v>
       </c>
       <c r="E3" t="n">
-        <v>7.237</v>
+        <v>4.5974</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.02</v>
+        <v>1.6732</v>
       </c>
       <c r="G3" t="n">
-        <v>2.53</v>
+        <v>1.2878</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7303</v>
+        <v>2.2483</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7998</v>
+        <v>-0.9605</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1679</v>
+        <v>1.8871</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7796</v>
+        <v>1.7754</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3883</v>
+        <v>0.1117</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6379</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0494</v>
+        <v>0.4729</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5885</v>
+        <v>-1.0722</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8147</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5143</v>
+        <v>2.2575</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5092</v>
+        <v>1.8971</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0051</v>
+        <v>0.3605</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1726</v>
+        <v>2.9529</v>
       </c>
       <c r="W3" t="n">
-        <v>3.3746</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2019</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.463</v>
+        <v>4.8885</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7199</v>
+        <v>3.49</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7431</v>
+        <v>1.3985</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6361</v>
+        <v>-1.652</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2454</v>
+        <v>1.2383</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.8815</v>
+        <v>-2.8902</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3058</v>
+        <v>-2.3462</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0906</v>
+        <v>-0.1109</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2152</v>
+        <v>-2.2353</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6697</v>
+        <v>0.6942</v>
       </c>
       <c r="N4" t="n">
-        <v>1.336</v>
+        <v>1.3492</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2236</v>
+        <v>1.6865</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4185</v>
+        <v>1.2586</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8051</v>
+        <v>0.428</v>
       </c>
       <c r="V4" t="n">
-        <v>6.0097</v>
+        <v>5.9921</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1024</v>
+        <v>7.0816</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0779</v>
+        <v>0.1055</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3028</v>
+        <v>-1.9903</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3807</v>
+        <v>2.0958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3163</v>
+        <v>0.339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4948</v>
+        <v>0.5022</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1785</v>
+        <v>-0.1632</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1612</v>
+        <v>0.1607</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1551</v>
+        <v>0.1784</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1785</v>
+        <v>-0.1669</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.5089</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6563</v>
+        <v>0.3419</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7546</v>
+        <v>1.7545</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0.662</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5391</v>
+        <v>-0.2164</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2236</v>
+        <v>-0.0362</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3155</v>
+        <v>-0.1802</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6407</v>
+        <v>-0.6322</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1876</v>
+        <v>-0.184</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4531</v>
+        <v>-0.4482</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6954</v>
+        <v>-0.6866</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.352</v>
+        <v>-0.0395</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>-0.0907</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.6367</v>
+        <v>-2.7285</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.0069</v>
+        <v>-2.6496</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3702</v>
+        <v>-0.0789</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5979</v>
+        <v>1.9208</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6724</v>
+        <v>1.1684</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.2702</v>
+        <v>0.7524</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9699</v>
+        <v>0.4382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7304</v>
+        <v>0.1929</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.7003</v>
+        <v>0.2453</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.628</v>
+        <v>1.4826</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9419</v>
+        <v>0.9755</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5699</v>
+        <v>0.5071</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-2.9592</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6683</v>
+        <v>0.4612</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8438</v>
+        <v>0.6454</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8244</v>
+        <v>-0.1841</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7997</v>
+        <v>-3.0618</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3856</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4141</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7717</v>
+        <v>-3.8765</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9974</v>
+        <v>-3.7896</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7743</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9076</v>
+        <v>-2.6027</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1585</v>
+        <v>1.6743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.749</v>
+        <v>-4.277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4565</v>
+        <v>-2.0062</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2007</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2558</v>
+        <v>-2.7194</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4511</v>
+        <v>-0.5965</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9578</v>
+        <v>0.9611</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4932</v>
+        <v>-1.5576</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9488</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5719</v>
+        <v>1.4287</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2662</v>
+        <v>1.1074</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8381</v>
+        <v>0.3212</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0658</v>
+        <v>-1.792</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.387</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2946</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.2137</v>
+        <v>-5.4069</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3298</v>
+        <v>-4.7723</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8839</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1841</v>
+        <v>-3.3593</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5626</v>
+        <v>0.4169</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3785</v>
+        <v>-3.7763</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0811</v>
+        <v>-2.0149</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2623</v>
+        <v>0.3168</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1812</v>
+        <v>-2.3317</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.103</v>
+        <v>-1.3444</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3003</v>
+        <v>0.1002</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1973</v>
+        <v>-1.4446</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.0011</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1785</v>
+        <v>-0.4324</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4335</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.6802</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8409</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7116</v>
+        <v>-5.4946</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2733</v>
+        <v>-3.4819</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4383</v>
+        <v>-2.0126</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3486</v>
+        <v>-2.1937</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4258</v>
+        <v>-2.5674</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7744</v>
+        <v>0.3737</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9896</v>
+        <v>-2.1086</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3321</v>
+        <v>-2.2795</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3218</v>
+        <v>0.1708</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.359</v>
+        <v>-0.0851</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.2879</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4526</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3215</v>
+        <v>0.5122</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9739</v>
+        <v>0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6524</v>
+        <v>0.4498</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.6749</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-2.8326</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3198</v>
+        <v>-5.6953</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6486</v>
+        <v>-8.2532</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3288</v>
+        <v>2.5579</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.946</v>
+        <v>-6.9518</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3377</v>
+        <v>-1.3356</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.6083</v>
+        <v>-5.6162</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.5021</v>
+        <v>-6.5409</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1469</v>
+        <v>-1.1623</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.3552</v>
+        <v>-5.3785</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4438</v>
+        <v>-0.4109</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.153</v>
+        <v>0.4809</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5172</v>
+        <v>-0.0702</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3641</v>
+        <v>0.551</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1402</v>
+        <v>2.1414</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>1.0476</v>
+        <v>1.052</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5481</v>
+        <v>-5.512600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.3926</v>
+        <v>-9.678899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8445</v>
+        <v>4.1664</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.3292</v>
+        <v>-11.3093</v>
       </c>
       <c r="H12" t="n">
-        <v>4.877199999999999</v>
+        <v>4.882299999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-16.2062</v>
+        <v>-16.1915</v>
       </c>
       <c r="J12" t="n">
-        <v>-8.1127</v>
+        <v>-8.342500000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4305</v>
+        <v>1.2997</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.5433</v>
+        <v>-9.642199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2164</v>
+        <v>-2.9666</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4463</v>
+        <v>3.5827</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.6629</v>
+        <v>-6.5494</v>
       </c>
       <c r="P12" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.5492</v>
+        <v>-21.625</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S12" t="n">
-        <v>7.5006</v>
+        <v>8.5716</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3251</v>
+        <v>5.407999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1755</v>
+        <v>3.1635</v>
       </c>
       <c r="V12" t="n">
-        <v>7.488</v>
+        <v>7.468499999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>14.9443</v>
+        <v>14.8806</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.4561</v>
+        <v>-7.411999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3996</v>
+        <v>5.5137</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2925</v>
+        <v>1.8518</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1072</v>
+        <v>3.662</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6423</v>
+        <v>4.6571</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0518</v>
+        <v>1.0594</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5905</v>
+        <v>3.5977</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1194</v>
+        <v>2.1007</v>
       </c>
       <c r="K13" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1914</v>
+        <v>1.1839</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5229</v>
+        <v>2.5564</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3991</v>
+        <v>2.4138</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8947</v>
+        <v>-1.8083</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6513</v>
+        <v>-1.0621</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2434</v>
+        <v>-0.7461</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4118</v>
+        <v>3.5413</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0766</v>
+        <v>2.7776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3352</v>
+        <v>0.7637</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9747</v>
+        <v>3.9536</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1574</v>
+        <v>1.1493</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8174</v>
+        <v>2.8044</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8027</v>
+        <v>3.7501</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5372</v>
+        <v>1.5094</v>
       </c>
       <c r="L14" t="n">
-        <v>2.2655</v>
+        <v>2.2408</v>
       </c>
       <c r="M14" t="n">
-        <v>0.172</v>
+        <v>0.2035</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2168</v>
+        <v>-0.0757</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0968</v>
+        <v>-0.3305</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1201</v>
+        <v>0.2548</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.638</v>
+        <v>3.5363</v>
       </c>
       <c r="E15" t="n">
-        <v>0.035</v>
+        <v>0.3565</v>
       </c>
       <c r="F15" t="n">
-        <v>2.603</v>
+        <v>3.1798</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5561</v>
+        <v>3.5703</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6636</v>
+        <v>1.6739</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8926</v>
+        <v>1.8965</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9855</v>
+        <v>0.9706</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1775</v>
+        <v>1.1721</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5706</v>
+        <v>2.5997</v>
       </c>
       <c r="N15" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O15" t="n">
-        <v>2.0846</v>
+        <v>2.098</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0542</v>
+        <v>-1.1706</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1644</v>
+        <v>-0.8111</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8898</v>
+        <v>-0.3595</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8305</v>
+        <v>1.3329</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6558</v>
+        <v>-2.2943</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4862</v>
+        <v>3.6273</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7584</v>
+        <v>0.7607</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3418</v>
+        <v>-2.3517</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1001</v>
+        <v>3.1124</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5914</v>
+        <v>-1.6234</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4497</v>
+        <v>-2.4798</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3497</v>
+        <v>2.384</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1079</v>
+        <v>0.1281</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2418</v>
+        <v>2.2559</v>
       </c>
       <c r="P16" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7238</v>
+        <v>-1.2228</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0968</v>
+        <v>-0.6858</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.627</v>
+        <v>-0.537</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6066</v>
+        <v>-1.6193</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0324</v>
+        <v>0.0149</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1221</v>
+        <v>0.6474</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2358</v>
+        <v>0.4582</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1138</v>
+        <v>0.1892</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6247</v>
+        <v>1.6254</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6998</v>
+        <v>0.7035</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8619</v>
+        <v>0.8486</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7628</v>
+        <v>0.7768</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7709</v>
+        <v>-0.2543</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1449</v>
+        <v>0.1361</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
@@ -1813,22 +1813,22 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1195</v>
+        <v>-0.1171</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1840,31 +1840,31 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5414</v>
+        <v>-0.5435</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5923</v>
+        <v>-0.4797</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2696</v>
+        <v>-4.0033</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3228</v>
+        <v>3.5237</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8043</v>
+        <v>-1.9113</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6204</v>
+        <v>-2.2799</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1839</v>
+        <v>0.3686</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0771</v>
+        <v>-2.5161</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2264</v>
+        <v>-1.9487</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1493</v>
+        <v>-0.5673</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7272</v>
+        <v>0.6048</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.394</v>
+        <v>-0.3312</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3331</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>2.9592</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6241</v>
+        <v>-0.5715</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0344</v>
+        <v>-0.2306</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5898</v>
+        <v>-0.341</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>1.5479</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>0.3007</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7024</v>
+        <v>-1.3252</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1746</v>
+        <v>-0.8653</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.877</v>
+        <v>-0.4599</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0891</v>
+        <v>-1.8011</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2063</v>
+        <v>-1.6226</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1172</v>
+        <v>-0.1785</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1411</v>
+        <v>-1.0856</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4342</v>
+        <v>-1.2345</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2931</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.948</v>
+        <v>-0.7155</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7721</v>
+        <v>-0.3881</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1759</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4378</v>
+        <v>0.8825</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3157</v>
+        <v>0.448</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1222</v>
+        <v>0.4345</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9393</v>
+        <v>-1.7594</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2902</v>
+        <v>-0.783</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3509</v>
+        <v>-0.9764</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8847</v>
+        <v>-2.09</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2711</v>
+        <v>-2.2031</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3864</v>
+        <v>0.113</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4617</v>
+        <v>-1.1588</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.923</v>
+        <v>-1.4414</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5387</v>
+        <v>0.2826</v>
       </c>
       <c r="M21" t="n">
-        <v>0.577</v>
+        <v>-0.9312</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.348</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>0.925</v>
+        <v>-0.1695</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0507</v>
+        <v>0.3714</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5867</v>
+        <v>0.3758</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.464</v>
+        <v>-0.0044</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5425</v>
+        <v>-1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2891</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4308</v>
+        <v>-1.8935</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1452</v>
+        <v>-2.3687</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2857</v>
+        <v>0.4751</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4256</v>
+        <v>2.4155</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.982</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4038</v>
+        <v>3.3975</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7181</v>
+        <v>1.6804</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.662</v>
+        <v>-0.6797</v>
       </c>
       <c r="L22" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7074</v>
+        <v>0.7351</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3101</v>
+        <v>-0.7643</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.234</v>
+        <v>-0.407</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0761</v>
+        <v>-0.3573</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.548100000000002</v>
+        <v>8.927</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6159</v>
+        <v>-4.940200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>11.1637</v>
+        <v>13.8674</v>
       </c>
       <c r="G23" t="n">
-        <v>11.3292</v>
+        <v>11.3092</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.8771</v>
+        <v>-4.8821</v>
       </c>
       <c r="I23" t="n">
-        <v>16.2063</v>
+        <v>16.1914</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2163</v>
+        <v>2.966499999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.446499999999999</v>
+        <v>-3.5825</v>
       </c>
       <c r="L23" t="n">
-        <v>6.6629</v>
+        <v>6.549300000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>8.1127</v>
+        <v>8.342599999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4305</v>
+        <v>-1.2996</v>
       </c>
       <c r="O23" t="n">
-        <v>9.5435</v>
+        <v>9.642200000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R23" t="n">
-        <v>21.549</v>
+        <v>21.6249</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.5007</v>
+        <v>-5.1571</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.1756</v>
+        <v>-3.1634</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.3251</v>
+        <v>-1.9937</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.4879</v>
+        <v>-7.468400000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>6.6849</v>
+        <v>6.638000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-14.1728</v>
+        <v>-14.1065</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104606_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104606_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.8326</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>1.052</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.411999999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.3007</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104606_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-14.1065</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
